--- a/CJFAS-Submission/Tables/TableA1.xlsx
+++ b/CJFAS-Submission/Tables/TableA1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\CHUMputerVisionProject\ManuscriptSubmission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F025BC-07FB-47A3-B2B8-76C5AC1C78EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3317CB1E-A332-4234-B8CB-F8E23D638D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31515" yWindow="3555" windowWidth="23415" windowHeight="16860" xr2:uid="{FCB07297-B30E-4E81-98A7-90071D94F4A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCB07297-B30E-4E81-98A7-90071D94F4A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,22 +137,76 @@
     <t>Loss</t>
   </si>
   <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>MSE</t>
+  </si>
+  <si>
+    <t>Batching</t>
+  </si>
+  <si>
+    <t>Batch size</t>
+  </si>
+  <si>
+    <t>Scheduling</t>
+  </si>
+  <si>
+    <t>Max epochs</t>
+  </si>
+  <si>
+    <t>80 - 150</t>
+  </si>
+  <si>
+    <t>Remaining epochs after phase 1</t>
+  </si>
+  <si>
+    <t>Max initial epochs</t>
+  </si>
+  <si>
+    <t>Early stopping</t>
+  </si>
+  <si>
+    <t>Patience</t>
+  </si>
+  <si>
+    <t>9 epochs</t>
+  </si>
+  <si>
+    <t>LR on plateau</t>
+  </si>
+  <si>
+    <t>Factor / patience / min LR</t>
+  </si>
+  <si>
+    <t>0.1 / 4 / 1e-12</t>
+  </si>
+  <si>
+    <t>Checkpointing</t>
+  </si>
+  <si>
+    <t>Monitor / policy</t>
+  </si>
+  <si>
+    <t>val_loss, best only</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Steps per epoch</t>
+  </si>
+  <si>
+    <t>len(x_train) // batch_size</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Mean Squared Error + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ℓ</t>
+      <t>Mean Squared Error + ℓ</t>
     </r>
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="12"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -160,75 +214,12 @@
       <t>2</t>
     </r>
   </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>Batching</t>
-  </si>
-  <si>
-    <t>Batch size</t>
-  </si>
-  <si>
-    <t>Scheduling</t>
-  </si>
-  <si>
-    <t>Max epochs</t>
-  </si>
-  <si>
-    <t>80 - 150</t>
-  </si>
-  <si>
-    <t>Remaining epochs after phase 1</t>
-  </si>
-  <si>
-    <t>Max initial epochs</t>
-  </si>
-  <si>
-    <t>Early stopping</t>
-  </si>
-  <si>
-    <t>Patience</t>
-  </si>
-  <si>
-    <t>9 epochs</t>
-  </si>
-  <si>
-    <t>LR on plateau</t>
-  </si>
-  <si>
-    <t>Factor / patience / min LR</t>
-  </si>
-  <si>
-    <t>0.1 / 4 / 1e-12</t>
-  </si>
-  <si>
-    <t>Checkpointing</t>
-  </si>
-  <si>
-    <t>Monitor / policy</t>
-  </si>
-  <si>
-    <t>val_loss, best only</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Steps per epoch</t>
-  </si>
-  <si>
-    <t>len(x_train) // batch_size</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,26 +229,20 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -646,7 +631,7 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="29.28515625" customWidth="1"/>
+    <col min="1" max="4" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -663,7 +648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -675,7 +660,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -687,7 +672,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -699,7 +684,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -787,7 +772,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -795,7 +780,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -804,45 +789,45 @@
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="2">
         <v>16</v>
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2">
         <v>50</v>
@@ -851,49 +836,49 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D20" s="2"/>
     </row>

--- a/CJFAS-Submission/Tables/TableA1.xlsx
+++ b/CJFAS-Submission/Tables/TableA1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rames\Documents\GitHub\chumputer-manuscript\CJFAS-Submission\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3317CB1E-A332-4234-B8CB-F8E23D638D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EC0D3F-0BED-44AD-9D9E-B3BAD39FA690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCB07297-B30E-4E81-98A7-90071D94F4A4}"/>
+    <workbookView xWindow="3330" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{AEB08D76-C810-40CC-B74C-D2C05A209B30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,189 +36,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
-    <t>Category</t>
+    <t xml:space="preserve">Agency </t>
   </si>
   <si>
-    <t>Setting</t>
+    <t>Total</t>
   </si>
   <si>
-    <t>Phase 1</t>
+    <t>ADF&amp;G</t>
   </si>
   <si>
-    <t>Phase 2: Fine-tuning</t>
+    <t>NOAA</t>
   </si>
   <si>
-    <t>Model backbone</t>
+    <t>DFO</t>
   </si>
   <si>
-    <t>Architecture</t>
+    <t>NSRAA</t>
   </si>
   <si>
-    <t>EfficientNetV2L, NASNetLarge, and ConvNeXtLarge (pretrained)</t>
+    <t>Model</t>
   </si>
   <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Input shape</t>
-  </si>
-  <si>
-    <t>(512, 512, 3)</t>
-  </si>
-  <si>
-    <t>Distribution</t>
-  </si>
-  <si>
-    <t>Strategy</t>
-  </si>
-  <si>
-    <t>tf.distribute.MirroredStrategy(). Use of both GPUs</t>
-  </si>
-  <si>
-    <t>Freezing</t>
-  </si>
-  <si>
-    <t>Layers frozen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First ⅓ of the network </t>
-  </si>
-  <si>
-    <t>All layers unfrozen</t>
-  </si>
-  <si>
-    <t>Model head</t>
-  </si>
-  <si>
-    <t>Pooling</t>
-  </si>
-  <si>
-    <t>GlobalAveragePooling2D</t>
-  </si>
-  <si>
-    <t>Dense layer</t>
-  </si>
-  <si>
-    <t>4096 units, ReLU</t>
-  </si>
-  <si>
-    <t>Dropout</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t>Final layer</t>
-  </si>
-  <si>
-    <t>Dense(1), linear</t>
-  </si>
-  <si>
-    <t>Optimizer</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>Learning rate</t>
-  </si>
-  <si>
-    <t>1e-5 (= LR × 0.1)</t>
-  </si>
-  <si>
-    <t>Loss/Metric</t>
-  </si>
-  <si>
-    <t>Loss</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>Batching</t>
-  </si>
-  <si>
-    <t>Batch size</t>
-  </si>
-  <si>
-    <t>Scheduling</t>
-  </si>
-  <si>
-    <t>Max epochs</t>
-  </si>
-  <si>
-    <t>80 - 150</t>
-  </si>
-  <si>
-    <t>Remaining epochs after phase 1</t>
-  </si>
-  <si>
-    <t>Max initial epochs</t>
-  </si>
-  <si>
-    <t>Early stopping</t>
-  </si>
-  <si>
-    <t>Patience</t>
-  </si>
-  <si>
-    <t>9 epochs</t>
-  </si>
-  <si>
-    <t>LR on plateau</t>
-  </si>
-  <si>
-    <t>Factor / patience / min LR</t>
-  </si>
-  <si>
-    <t>0.1 / 4 / 1e-12</t>
-  </si>
-  <si>
-    <t>Checkpointing</t>
-  </si>
-  <si>
-    <t>Monitor / policy</t>
-  </si>
-  <si>
-    <t>val_loss, best only</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Steps per epoch</t>
-  </si>
-  <si>
-    <t>len(x_train) // batch_size</t>
-  </si>
-  <si>
-    <r>
-      <t>Mean Squared Error + ℓ</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>Age Label</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -229,7 +80,13 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -237,15 +94,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -280,22 +131,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -627,262 +493,350 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35987FDF-3080-4EA3-B63F-952081B533E1}">
-  <dimension ref="A1:D20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEDCD52-0B92-4746-97DB-2ABF488B8008}">
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="G2" s="2">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="2">
         <v>6</v>
       </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I2" s="2">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3">
+        <v>26208</v>
+      </c>
+      <c r="G3" s="3">
+        <v>23873</v>
+      </c>
+      <c r="H3" s="3">
+        <v>143</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="4">
+        <v>50241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>144</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3748</v>
+      </c>
+      <c r="F4" s="3">
+        <v>7355</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1254</v>
+      </c>
+      <c r="H4" s="3">
+        <v>110</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4">
+        <v>12617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3">
+        <v>207</v>
+      </c>
+      <c r="D5" s="3">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>431</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1963</v>
+      </c>
+      <c r="H5" s="3">
+        <v>51</v>
+      </c>
+      <c r="I5" s="3">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="J5" s="4">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3">
+        <v>241</v>
+      </c>
+      <c r="F6" s="3">
+        <v>278</v>
+      </c>
+      <c r="G6" s="3">
+        <v>71</v>
+      </c>
+      <c r="H6" s="3">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="4">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>208</v>
+      </c>
+      <c r="D7" s="3">
+        <v>179</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4009</v>
+      </c>
+      <c r="F7" s="3">
+        <v>34272</v>
+      </c>
+      <c r="G7" s="3">
+        <v>27161</v>
+      </c>
+      <c r="H7" s="3">
+        <v>311</v>
+      </c>
+      <c r="I7" s="3">
+        <v>13</v>
+      </c>
+      <c r="J7" s="4">
+        <v>66153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2487</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3447</v>
+      </c>
+      <c r="H8" s="3">
+        <v>142</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="4">
+        <v>6093</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>88</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3720</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3333</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1249</v>
+      </c>
+      <c r="H9" s="3">
+        <v>83</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5</v>
+      </c>
+      <c r="J9" s="4">
+        <v>8479</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3">
+        <v>178</v>
+      </c>
+      <c r="D10" s="3">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>382</v>
+      </c>
+      <c r="H10" s="3">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6</v>
+      </c>
+      <c r="J10" s="4">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
+        <v>224</v>
+      </c>
+      <c r="F11" s="3">
+        <v>270</v>
+      </c>
+      <c r="G11" s="3">
+        <v>64</v>
+      </c>
+      <c r="H11" s="3">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>179</v>
+      </c>
+      <c r="D12" s="3">
+        <v>118</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3961</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6095</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5142</v>
+      </c>
+      <c r="H12" s="3">
+        <v>248</v>
+      </c>
+      <c r="I12" s="3">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1E-4</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="2">
-        <v>50</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="2"/>
+      <c r="J12" s="4">
+        <v>15754</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="C1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>